--- a/forms/trg/Formulir_TRG_safos.xlsx
+++ b/forms/trg/Formulir_TRG_safos.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B33)</f>
+        <f>COUNTA(Anggota!B5:B34)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F33)</f>
+        <f>COUNTA(Anggota!F5:F34)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Rinaldi Sjahril</t>
+          <t>Prof. Dr. Ir. Dorothea Agnes Rampisela, M.Sc.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -926,11 +926,7 @@
           <t>Universitas Hasanuddin</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Biotechnology and Cultivation</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -950,12 +946,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Syamsul Arifin Lias</t>
+          <t>Prof. Rinaldi Sjahril</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,7 +961,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Soil and Water Conservation</t>
+          <t>Biotechnology and Cultivation</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Fauzan Adzima</t>
+          <t>Syamsul Arifin Lias</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,7 +998,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Geography, Soil Conservation, and Remote Sensing</t>
+          <t>Soil and Water Conservation</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,12 +1020,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Risky Nurhikmayani</t>
+          <t>Ahmad Fauzan Adzima</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1039,7 +1035,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Geography, Soil Conservation, and Remote Sensing</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,12 +1057,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ahyar</t>
+          <t>Risky Nurhikmayani</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1076,7 +1072,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Chemistry and Enzymatic Processes of Starch</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,18 +1094,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Novaty Eny Dungga</t>
+          <t>Prof. Ahyar</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Horticulture</t>
+          <t>Chemistry and Enzymatic Processes of Starch</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1131,22 +1131,18 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ohte Nobuhito</t>
+          <t>Dr. Novaty Eny Dungga</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Kyoto University, Japan</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Environmental science/Agricultural science / Rural Environmental Engineering and Planning</t>
+          <t>Horticulture</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1168,22 +1164,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. Shimagami Motoko</t>
+          <t>Prof. Ohte Nobuhito</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Kyoto University, Japan</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Institute for International Relations, Ehime University</t>
+          <t>Environmental science/Agricultural science / Rural Environmental Engineering and Planning</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1205,22 +1201,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Oktaviani Nelsi, S.Hut</t>
+          <t>Prof. Shimagami Motoko</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Kagawa University, Japan</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Soil Biodiversity</t>
+          <t>Institute for International Relations, Ehime University</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1242,18 +1238,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Widya Kamma, S.P., M.Sc.</t>
+          <t>Oktaviani Nelsi, S.Hut</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Kagawa University, Japan</t>
+        </is>
+      </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Soil Chemical, Soil Biodiversity</t>
+          <t>Soil Biodiversity</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1275,16 +1275,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Tahnur</t>
+          <t>Widya Kamma, S.P., M.Sc.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Soil Chemical, Soil Biodiversity</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1304,12 +1308,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Sarlan</t>
+          <t>Muhammad Tahnur</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1333,24 +1337,16 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Prof. Samuel Arung Paembonan</t>
+          <t>Sarlan</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Agroforestry and Carbon Sequestration</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1370,12 +1366,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Darmawan Salman</t>
+          <t>Prof. Samuel Arung Paembonan</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1385,7 +1381,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Socio Economic Value of Agriculture Commodities</t>
+          <t>Agroforestry and Carbon Sequestration</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1407,12 +1403,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Prof. Meta Mahendratta</t>
+          <t>Prof. Dr. Ir. Darmawan Salman</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1422,7 +1418,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Food Technology for Special Needs Children</t>
+          <t>Socio Economic Value of Agriculture Commodities</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1444,12 +1440,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Dr. Mahyuddin</t>
+          <t>Prof. Meta Mahendratta</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1459,7 +1455,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Socio Economic Value of Agriculture Commodities</t>
+          <t>Food Technology for Special Needs Children</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1481,12 +1477,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sawedi Muhammad</t>
+          <t>Dr. Mahyuddin</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1496,7 +1492,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Sociology of Conflict and Community Development</t>
+          <t>Socio Economic Value of Agriculture Commodities</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1516,10 +1512,26 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="11" t="n"/>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Dr. Sawedi Muhammad</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Sociology of Conflict and Community Development</t>
+        </is>
+      </c>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
@@ -1527,7 +1539,11 @@
       <c r="J22" s="12" t="n"/>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1716,15 +1732,32 @@
       <c r="L33" s="12" t="n"/>
       <c r="M33" s="12" t="n"/>
     </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
